--- a/src/cubes/data/energy_systems/electric-vehicles.xlsx
+++ b/src/cubes/data/energy_systems/electric-vehicles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/energy_systems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB75E4E-2D05-B846-9E68-4872D3334E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABEBC16-50F8-9A43-8A57-A8A8550DA34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9280" yWindow="3560" windowWidth="27640" windowHeight="16940" xr2:uid="{05058415-C571-004D-A5F9-9C4ED88F80E6}"/>
   </bookViews>
@@ -179,16 +179,16 @@
     <t>COUNTRY TOTAL VEHICLES</t>
   </si>
   <si>
-    <t>COUNTRY PERCENTAGE BEVS</t>
-  </si>
-  <si>
-    <t>COUNTRY PERCENTAGE PHEVS</t>
-  </si>
-  <si>
     <t>BEV MAXIMUM BATTERY SIZE (kWh)</t>
   </si>
   <si>
     <t>PHEV MAXIMUM BATTERY SIZE (kWh)</t>
+  </si>
+  <si>
+    <t>COUNTRY PROBABILITY BEVS</t>
+  </si>
+  <si>
+    <t>COUNTRY PROBABILITY PHEVS</t>
   </si>
 </sst>
 </file>
@@ -243,7 +243,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,22 +641,22 @@
         <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
